--- a/storage/stats/joker/Joker_2026.xlsx
+++ b/storage/stats/joker/Joker_2026.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -20,89 +20,125 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="45">
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
   <si>
     <t xml:space="preserve">44</t>
   </si>
   <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
     <t xml:space="preserve">39</t>
   </si>
   <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
     <t xml:space="preserve">21</t>
   </si>
   <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
     <t xml:space="preserve">45</t>
   </si>
   <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
     <t xml:space="preserve">25</t>
   </si>
   <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
     <t xml:space="preserve">17</t>
   </si>
   <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
     <t xml:space="preserve">27</t>
   </si>
   <si>
@@ -112,49 +148,13 @@
     <t xml:space="preserve">43</t>
   </si>
   <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
     <t xml:space="preserve">20</t>
   </si>
   <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
     <t xml:space="preserve">36</t>
   </si>
   <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
     <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
   </si>
 </sst>
 </file>
@@ -263,37 +263,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -366,7 +366,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -397,253 +397,253 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="D5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="C14" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>19</v>
@@ -651,442 +651,442 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="E26" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E35" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1094,416 +1094,416 @@
         <v>26</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="C45" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="C46" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F46" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="F48" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>0</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E51" s="1" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="F54" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>16</v>
@@ -1511,339 +1511,339 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F66" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="E68" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F73" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>25</v>
@@ -1851,282 +1851,462 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C82" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C83" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C84" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D85" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B94" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F88" s="1" t="s">
+      <c r="F94" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>26</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/storage/stats/joker/Joker_2026.xlsx
+++ b/storage/stats/joker/Joker_2026.xlsx
@@ -20,41 +20,89 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="45">
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
   <si>
     <t xml:space="preserve">32</t>
   </si>
   <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
     <t xml:space="preserve">41</t>
   </si>
   <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
     <t xml:space="preserve">38</t>
   </si>
   <si>
     <t xml:space="preserve">19</t>
   </si>
   <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
     <t xml:space="preserve">31</t>
   </si>
   <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
@@ -67,94 +115,46 @@
     <t xml:space="preserve">12</t>
   </si>
   <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
     <t xml:space="preserve">16</t>
   </si>
   <si>
     <t xml:space="preserve">13</t>
   </si>
   <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
     <t xml:space="preserve">15</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
   </si>
   <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
     <t xml:space="preserve">29</t>
   </si>
   <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
     <t xml:space="preserve">8</t>
   </si>
   <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
     <t xml:space="preserve">37</t>
   </si>
   <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
     <t xml:space="preserve">26</t>
   </si>
   <si>
     <t xml:space="preserve">23</t>
   </si>
   <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
     <t xml:space="preserve">21</t>
   </si>
   <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
     <t xml:space="preserve">25</t>
   </si>
   <si>
     <t xml:space="preserve">17</t>
   </si>
   <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
     <t xml:space="preserve">40</t>
   </si>
   <si>
     <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
   </si>
 </sst>
 </file>
@@ -366,7 +366,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -397,24 +397,24 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>13</v>
@@ -431,16 +431,16 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>19</v>
@@ -451,399 +451,399 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -851,339 +851,339 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="F25" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="D30" s="1" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="F32" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="F34" s="1" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>10</v>
@@ -1191,1039 +1191,1039 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="F46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="D52" s="1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C75" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D81" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F81" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D85" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D86" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D93" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>31</v>
@@ -2231,47 +2231,47 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>20</v>
@@ -2280,33 +2280,133 @@
         <v>26</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E97" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>18</v>
+      <c r="B99" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/storage/stats/joker/Joker_2026.xlsx
+++ b/storage/stats/joker/Joker_2026.xlsx
@@ -20,7 +20,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="45">
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
   <si>
     <t xml:space="preserve">24</t>
   </si>
@@ -46,9 +64,6 @@
     <t xml:space="preserve">27</t>
   </si>
   <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
     <t xml:space="preserve">22</t>
   </si>
   <si>
@@ -70,9 +85,6 @@
     <t xml:space="preserve">44</t>
   </si>
   <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
     <t xml:space="preserve">34</t>
   </si>
   <si>
@@ -124,9 +136,6 @@
     <t xml:space="preserve">15</t>
   </si>
   <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
     <t xml:space="preserve">29</t>
   </si>
   <si>
@@ -142,16 +151,7 @@
     <t xml:space="preserve">23</t>
   </si>
   <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
     <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
   </si>
   <si>
     <t xml:space="preserve">43</t>
@@ -366,7 +366,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -397,41 +397,41 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>17</v>
@@ -440,553 +440,553 @@
         <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -994,119 +994,119 @@
         <v>20</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="E35" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F36" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1114,1299 +1114,1319 @@
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="C43" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E47" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="E57" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="F60" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C62" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="E62" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F63" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="D66" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F66" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D70" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F70" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F71" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="D73" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D90" s="1" t="s">
+      <c r="E90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F94" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/storage/stats/joker/Joker_2026.xlsx
+++ b/storage/stats/joker/Joker_2026.xlsx
@@ -20,11 +20,56 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="45">
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
   <si>
     <t xml:space="preserve">21</t>
   </si>
   <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
     <t xml:space="preserve">25</t>
   </si>
   <si>
@@ -43,18 +88,6 @@
     <t xml:space="preserve">24</t>
   </si>
   <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
     <t xml:space="preserve">7</t>
   </si>
   <si>
@@ -70,21 +103,12 @@
     <t xml:space="preserve">18</t>
   </si>
   <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
     <t xml:space="preserve">36</t>
   </si>
   <si>
     <t xml:space="preserve">45</t>
   </si>
   <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
     <t xml:space="preserve">34</t>
   </si>
   <si>
@@ -100,9 +124,6 @@
     <t xml:space="preserve">39</t>
   </si>
   <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
     <t xml:space="preserve">41</t>
   </si>
   <si>
@@ -115,43 +136,22 @@
     <t xml:space="preserve">31</t>
   </si>
   <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
     <t xml:space="preserve">35</t>
   </si>
   <si>
     <t xml:space="preserve">12</t>
   </si>
   <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
     <t xml:space="preserve">13</t>
   </si>
   <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
     <t xml:space="preserve">29</t>
   </si>
   <si>
     <t xml:space="preserve">8</t>
   </si>
   <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
     <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
   </si>
   <si>
     <t xml:space="preserve">43</t>
@@ -366,7 +366,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -406,24 +406,24 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>15</v>
@@ -431,322 +431,322 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -754,456 +754,456 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="E29" s="1" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D30" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="E31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F33" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="E34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="F36" s="1" t="s">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F38" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F41" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>15</v>
@@ -1211,1042 +1211,1042 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="D54" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="D57" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="F61" s="1" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F62" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C63" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="C70" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F73" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E86" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C90" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E90" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2254,19 +2254,19 @@
         <v>13</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2274,159 +2274,219 @@
         <v>43</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="D99" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C104" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>36</v>
+      <c r="F106" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
